--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.91.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.91.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.91.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0091.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0091.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,19 +605,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+2022 BULLET, U+FFFD REPLACEMENT CHARACTER :: knj ï½• n Ñ�Ï„ o Ï„ s.</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+FF55 FULLWIDTH LATIN SMALL LETTER U :: knj ｕ n сτ o τ s.</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tween common and special injunctions, see Danielâ€™s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ground th</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ground th</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L18: stray/suspicious non-ASCII glyph(s): U+7A97 CJK UNIFIED IDEOGRAPH-7A97 | isolated marker/symbol line :: 窗</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -649,7 +653,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,19 +668,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L18: stray/suspicious non-ASCII glyph(s): U+7A97 CJK UNIFIED IDEOGRAPH-7A97 | isolated marker/symbol line :: 窗</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: common injunctions :â€”</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: of answer, on or after the expiration of fourteen days from•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: ,</t>
+          <t>L19: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -719,19 +723,15 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: in of fourteen days from the service of the subpoenaÃ¦ena ;</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: of answer, on or after the expiration of fourteen days fromâ€¢</t>
-        </is>
-      </c>
+          <t>L19: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L31: symbol-only separator/garbage line :: 1850.</t>
+          <t>L28: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -778,7 +778,7 @@
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: S</t>
+          <t>L31: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -825,7 +825,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 8</t>
+          <t>L56: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -868,7 +868,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 2</t>
+          <t>L78: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -909,7 +909,11 @@
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L79: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
@@ -974,7 +978,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1047,7 +1051,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
